--- a/datos/resultados.xlsx
+++ b/datos/resultados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,20 +439,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cli_ciudad</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>cantidad</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>prod_precio</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>importe</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
@@ -477,16 +482,21 @@
           <t>Sofia</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Zapopan</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1800</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>3600</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
@@ -511,16 +521,21 @@
           <t>Miguel</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>1800</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>5400</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
@@ -545,16 +560,21 @@
           <t>Miguel</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1800</v>
       </c>
       <c r="G4" t="n">
         <v>1800</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
@@ -579,16 +599,21 @@
           <t>Maria</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8500</v>
       </c>
       <c r="G5" t="n">
         <v>8500</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
@@ -613,16 +638,21 @@
           <t>Carlos</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>15000</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>30000</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
@@ -647,16 +677,21 @@
           <t>Jose</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>1400</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>2800</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
@@ -681,16 +716,21 @@
           <t>Jorge</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1400</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>2800</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
@@ -715,16 +755,21 @@
           <t>Miguel</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>25000</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>75000</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
@@ -749,16 +794,21 @@
           <t>Alejandro</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2000</v>
       </c>
       <c r="G10" t="n">
         <v>2000</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>2026-01-23</t>
         </is>
@@ -783,16 +833,21 @@
           <t>Maria</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>8000</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>24000</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
@@ -817,16 +872,21 @@
           <t>Alejandro</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Zapopan</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>25000</v>
       </c>
       <c r="G12" t="n">
         <v>25000</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
@@ -851,16 +911,21 @@
           <t>Diego</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Merida</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>25000</v>
       </c>
       <c r="G13" t="n">
         <v>25000</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
@@ -885,16 +950,21 @@
           <t>Jorge</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>San Luis Potosi</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>6000</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>12000</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
@@ -919,16 +989,21 @@
           <t>Jorge</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>San Luis Potosi</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>2000</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>4000</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
@@ -953,16 +1028,21 @@
           <t>Miguel</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>1800</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>5400</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
@@ -987,16 +1067,21 @@
           <t>Raul</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>4500</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>9000</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>2026-01-20</t>
         </is>
@@ -1021,16 +1106,21 @@
           <t>Jorge</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>San Luis Potosi</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>4500</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>9000</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
@@ -1055,16 +1145,21 @@
           <t>Marta</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>2000</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>4000</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
@@ -1089,16 +1184,21 @@
           <t>Alejandro</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Zapopan</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>3</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>600</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>1800</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
@@ -1123,16 +1223,21 @@
           <t>Sofia</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Zapopan</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>15000</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>30000</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
@@ -1157,16 +1262,21 @@
           <t>Sofia</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>600</v>
       </c>
       <c r="G22" t="n">
         <v>600</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" t="n">
+        <v>600</v>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
@@ -1191,16 +1301,21 @@
           <t>Jorge</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>5500</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>11000</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -1225,16 +1340,21 @@
           <t>Juan</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>5500</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>16500</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
@@ -1259,16 +1379,21 @@
           <t>Jorge</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>2</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>1500</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>3000</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
@@ -1293,16 +1418,21 @@
           <t>Miguel</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1800</v>
       </c>
       <c r="G26" t="n">
         <v>1800</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
@@ -1327,16 +1457,21 @@
           <t>Sofia</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Zapopan</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>8000</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>16000</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
@@ -1361,16 +1496,21 @@
           <t>Elena</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>1400</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>2800</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
@@ -1395,16 +1535,21 @@
           <t>Sara</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Zapopan</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>8000</v>
       </c>
       <c r="G29" t="n">
         <v>8000</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
@@ -1429,16 +1574,21 @@
           <t>Maria</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CDMX</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1500</v>
       </c>
       <c r="G30" t="n">
         <v>1500</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
